--- a/data/SI/SI_2_site_selection.xlsx
+++ b/data/SI/SI_2_site_selection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/SI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="371" documentId="8_{EF4B609D-3C32-4D85-B6D7-614095F206BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02ACB667-0E23-47D2-BBC6-8C0A7056C65F}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="8_{EF4B609D-3C32-4D85-B6D7-614095F206BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88FCCE22-8478-4D66-BAFC-621892BC3BE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B09C33A3-69AE-4EDE-B293-E9623AD2B114}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B09C33A3-69AE-4EDE-B293-E9623AD2B114}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -3028,6 +3028,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B231D443-D3C4-4EF0-BDC9-8F5B03D7CAA5}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:DR68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3182,7 +3183,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
@@ -3261,7 +3262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>56</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>72</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>29.039084533163262</v>
       </c>
     </row>
-    <row r="6" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>76</v>
       </c>
@@ -3596,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>81</v>
       </c>
@@ -3687,7 +3688,7 @@
         <v>3.5165997959183577</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>84</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>101</v>
       </c>
@@ -3955,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>107</v>
       </c>
@@ -4049,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>109</v>
       </c>
@@ -4140,7 +4141,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>112</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v>2.7760508515306124</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>114</v>
       </c>
@@ -4319,7 +4320,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>116</v>
       </c>
@@ -4407,7 +4408,7 @@
         <v>0.12428704693877551</v>
       </c>
     </row>
-    <row r="16" spans="1:38" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>119</v>
       </c>
@@ -4497,7 +4498,7 @@
         <v>1.4536125510204081</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>122</v>
       </c>
@@ -4585,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>127</v>
       </c>
@@ -4679,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>129</v>
       </c>
@@ -4770,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>135</v>
       </c>
@@ -4864,7 +4865,7 @@
         <v>4.4745421183166938</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>140</v>
       </c>
@@ -4952,7 +4953,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>142</v>
       </c>
@@ -5120,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>153</v>
       </c>
@@ -5208,7 +5209,7 @@
         <v>4.1704080612244905</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>155</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>164</v>
       </c>
@@ -5399,7 +5400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>169</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>1.2201776096938775</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>171</v>
       </c>
@@ -5581,7 +5582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>176</v>
       </c>
@@ -5672,7 +5673,7 @@
         <v>7.932820721938775</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>178</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>189</v>
       </c>
@@ -5934,7 +5935,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>191</v>
       </c>
@@ -6022,7 +6023,7 @@
         <v>1.0473627551020408</v>
       </c>
     </row>
-    <row r="34" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>193</v>
       </c>
@@ -6102,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>199</v>
       </c>
@@ -6184,7 +6185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>205</v>
       </c>
@@ -6275,7 +6276,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>207</v>
       </c>
@@ -6366,7 +6367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>210</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>213</v>
       </c>
@@ -6545,7 +6546,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>215</v>
       </c>
@@ -6636,7 +6637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>217</v>
       </c>
@@ -6724,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>220</v>
       </c>
@@ -6885,7 +6886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>231</v>
       </c>
@@ -6973,7 +6974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>234</v>
       </c>
@@ -7067,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>238</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>240</v>
       </c>
@@ -7249,7 +7250,7 @@
         <v>0.15869132653061224</v>
       </c>
     </row>
-    <row r="48" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" s="10" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>243</v>
       </c>
@@ -7336,7 +7337,7 @@
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>246</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>249</v>
       </c>
@@ -7590,7 +7591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>257</v>
       </c>
@@ -7749,7 +7750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>266</v>
       </c>
@@ -7837,7 +7838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>270</v>
       </c>
@@ -7999,7 +8000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>276</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>279</v>
       </c>
@@ -8178,7 +8179,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>281</v>
       </c>
@@ -8266,7 +8267,7 @@
         <v>5.8747529081632548</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" t="s">
         <v>283</v>
@@ -8358,7 +8359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" t="s">
         <v>289</v>
@@ -8450,7 +8451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
       <c r="B62" t="s">
         <v>290</v>
@@ -8542,7 +8543,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" t="s">
         <v>293</v>
@@ -8631,7 +8632,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" t="s">
         <v>295</v>
@@ -8720,7 +8721,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="65" spans="1:122" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:122" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" t="s">
         <v>297</v>
@@ -8809,7 +8810,7 @@
         <v>1.2300799484693878</v>
       </c>
     </row>
-    <row r="66" spans="1:122" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:122" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22"/>
       <c r="B66" s="23" t="s">
         <v>299</v>
@@ -9103,7 +9104,13 @@
       <c r="DR68" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:DR66" xr:uid="{B231D443-D3C4-4EF0-BDC9-8F5B03D7CAA5}"/>
+  <autoFilter ref="A1:DR66" xr:uid="{B231D443-D3C4-4EF0-BDC9-8F5B03D7CAA5}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="manufacturing"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/data/SI/SI_2_site_selection.xlsx
+++ b/data/SI/SI_2_site_selection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/SI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="567" documentId="8_{EF4B609D-3C32-4D85-B6D7-614095F206BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32613188-20C5-4B42-AEEA-733C73F21182}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="8_{EF4B609D-3C32-4D85-B6D7-614095F206BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B3B1800-A1C0-4A57-8EE1-C08F8357BB09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B09C33A3-69AE-4EDE-B293-E9623AD2B114}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{B09C33A3-69AE-4EDE-B293-E9623AD2B114}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="concentrate_grade" sheetId="8" r:id="rId5"/>
     <sheet name="prices" sheetId="3" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">concentrate_grade!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">market_shares!$A$1:$F$44</definedName>
@@ -49,24 +46,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={DBCEC4D1-B66A-4062-8D3C-4D8C9DFFB5A5}</author>
-  </authors>
-  <commentList>
-    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{DBCEC4D1-B66A-4062-8D3C-4D8C9DFFB5A5}">
-      <text>
-        <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    Not presented in the final results because of outliers values for human tox</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="287">
   <si>
@@ -584,9 +563,6 @@
   </si>
   <si>
     <t>Not sure (no GHG)</t>
-  </si>
-  <si>
-    <t>HS code</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -1054,6 +1030,9 @@
   </si>
   <si>
     <t>Underground mining and beneficiation at Red Lake</t>
+  </si>
+  <si>
+    <t>Commodity name</t>
   </si>
 </sst>
 </file>
@@ -1325,597 +1304,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="prod_$_data"/>
-      <sheetName val="README"/>
-      <sheetName val="site_selection"/>
-      <sheetName val="prod_data"/>
-      <sheetName val="market_shares"/>
-      <sheetName val="concentrate_grade"/>
-      <sheetName val="prod_table_raw"/>
-      <sheetName val="site_selection_1"/>
-      <sheetName val="ms_benchmark"/>
-      <sheetName val="Arch_refineries"/>
-      <sheetName val="archetypes"/>
-      <sheetName val="prices"/>
-      <sheetName val="ta_data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5">
-        <row r="4">
-          <cell r="F4">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>51</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="F8">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="F9">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="F10">
-            <v>85</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="13">
-          <cell r="N13">
-            <v>166000</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="N14">
-            <v>0.90200150000000001</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="N17">
-            <v>17332900</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="N18">
-            <v>18.785114342499998</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="N19">
-            <v>9.6731885000000002</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="N22">
-            <v>2.6935630999999902</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="N23">
-            <v>0.7527047</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="N24">
-            <v>1361450</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="N35">
-            <v>0.27520376799999902</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="N36">
-            <v>6862152</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="N38">
-            <v>6.7893341869999997</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="N39">
-            <v>19050</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="N48">
-            <v>25434853.502416398</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="N49">
-            <v>21.070941660999999</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="N50">
-            <v>2.4571765000000001</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="N54">
-            <v>2.7205298345000002</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="N55">
-            <v>222627</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="N59">
-            <v>7.2160120000000001</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="N60">
-            <v>0.36810992249999902</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="N62">
-            <v>1661000</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="N80">
-            <v>30000000</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="N81">
-            <v>545.21758399999999</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="N82">
-            <v>55610.379200000003</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="N85">
-            <v>39.036757999999999</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="N86">
-            <v>2886927.3287240001</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="N87">
-            <v>4.3850512759503602</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="N91">
-            <v>1266009</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="N92">
-            <v>4.3869931575000001</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="N93">
-            <v>17408000</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="N94">
-            <v>900</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="N95">
-            <v>102400</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="N100">
-            <v>8.0869099999999996</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="N101">
-            <v>2911000</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="N103">
-            <v>4.0869999000000004</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="N105">
-            <v>439008</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="N113">
-            <v>22600</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="N114">
-            <v>38600</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="N115">
-            <v>42.860622999999997</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="N116">
-            <v>1340000</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="N119">
-            <v>1.1053250795</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="N120">
-            <v>191148</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="N121">
-            <v>9.0448977999999999E-2</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="N130">
-            <v>1526729</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="N135">
-            <v>2.2666986659999999</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="N136">
-            <v>7702.4385169999996</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="N137">
-            <v>2577.9603750000001</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="N138">
-            <v>7.3401460684999904</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="N139">
-            <v>1501500</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="N146">
-            <v>441588</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="N147">
-            <v>7.1082383724999998</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="N148">
-            <v>1.0264154999999999</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="N150">
-            <v>1165551</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="N152">
-            <v>6123.4920000000002</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="N153">
-            <v>98408.871032543204</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="N154">
-            <v>43726.856187782003</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="N155">
-            <v>8164.6559999999999</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="N160">
-            <v>3842649.0057279998</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="N161">
-            <v>13.426311830047601</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="N162">
-            <v>3.8879375</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="N163">
-            <v>1918143</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="N164">
-            <v>11.326059593499901</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="N165">
-            <v>0.8397945</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="N171">
-            <v>28060.108304000001</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="N173">
-            <v>4.8021004684999999</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="N175">
-            <v>21680000</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="N178">
-            <v>1.301183819</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="N179">
-            <v>5948239</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="N180">
-            <v>13673.530839999999</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="N183">
-            <v>1028000</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="N184">
-            <v>5.59863</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="N187">
-            <v>2.0974023155000001</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="N189">
-            <v>3065000</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="N190">
-            <v>21500.2608</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="N193">
-            <v>596912</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="N200">
-            <v>40926</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="N201">
-            <v>58100</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="N202">
-            <v>6835294.1176470499</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="N203">
-            <v>5488</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="N204">
-            <v>24232</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="N205">
-            <v>498</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="N206">
-            <v>4.4160749299999997</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="N207">
-            <v>1500000</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="N211">
-            <v>8764000</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="N212">
-            <v>7.8923576074999904</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="N229">
-            <v>122000</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="N231">
-            <v>1.2054783495000001</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="N232">
-            <v>5.8276450705</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="N233">
-            <v>26.4915663305</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="N234">
-            <v>34642</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="N235">
-            <v>12154</v>
-          </cell>
-        </row>
-        <row r="248">
-          <cell r="N248">
-            <v>4700</v>
-          </cell>
-        </row>
-        <row r="249">
-          <cell r="N249">
-            <v>7900</v>
-          </cell>
-        </row>
-        <row r="250">
-          <cell r="N250">
-            <v>464705.88235294097</v>
-          </cell>
-        </row>
-        <row r="254">
-          <cell r="N254">
-            <v>1574000</v>
-          </cell>
-        </row>
-        <row r="255">
-          <cell r="N255">
-            <v>4.1336551500000001</v>
-          </cell>
-        </row>
-        <row r="266">
-          <cell r="N266">
-            <v>9600</v>
-          </cell>
-        </row>
-        <row r="267">
-          <cell r="N267">
-            <v>13500</v>
-          </cell>
-        </row>
-        <row r="268">
-          <cell r="N268">
-            <v>794117.64705882303</v>
-          </cell>
-        </row>
-        <row r="271">
-          <cell r="N271">
-            <v>1034000</v>
-          </cell>
-        </row>
-        <row r="273">
-          <cell r="N273">
-            <v>2.8926254999999998</v>
-          </cell>
-        </row>
-        <row r="274">
-          <cell r="N274">
-            <v>1.1431780389999999</v>
-          </cell>
-        </row>
-        <row r="275">
-          <cell r="N275">
-            <v>5.7572578499999896</v>
-          </cell>
-        </row>
-        <row r="277">
-          <cell r="N277">
-            <v>2878047</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Marin Pellan" id="{6181ACFA-18AD-48AE-8FBC-D51C625C72F5}" userId="S::marin.pellan@polymtl.ca::3f7c0edb-e8ec-4a37-8825-7980f4e34b60" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2233,80 +1623,72 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D36" dT="2026-01-29T13:26:08.53" personId="{6181ACFA-18AD-48AE-8FBC-D51C625C72F5}" id="{DBCEC4D1-B66A-4062-8D3C-4D8C9DFFB5A5}">
-    <text>Not presented in the final results because of outliers values for human tox</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9AB529A-450A-4FA4-9C91-381D7C8AD79B}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="138.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="3" spans="1:2" ht="64" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="8" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="64.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="B5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
         <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="B6" s="10">
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" t="s">
         <v>267</v>
-      </c>
-      <c r="B7" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -2315,44 +1697,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B231D443-D3C4-4EF0-BDC9-8F5B03D7CAA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B231D443-D3C4-4EF0-BDC9-8F5B03D7CAA5}">
   <dimension ref="A1:AL40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.85546875" customWidth="1"/>
-    <col min="8" max="8" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.81640625" customWidth="1"/>
+    <col min="8" max="8" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="50.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.54296875" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="11.85546875" customWidth="1"/>
-    <col min="20" max="20" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.42578125" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="9.85546875" customWidth="1"/>
-    <col min="30" max="30" width="11.85546875" customWidth="1"/>
-    <col min="31" max="31" width="11.5703125" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" customWidth="1"/>
-    <col min="36" max="36" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="11.81640625" customWidth="1"/>
+    <col min="20" max="20" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.453125" customWidth="1"/>
+    <col min="22" max="22" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="9.81640625" customWidth="1"/>
+    <col min="30" max="30" width="11.81640625" customWidth="1"/>
+    <col min="31" max="31" width="11.54296875" customWidth="1"/>
+    <col min="32" max="32" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.81640625" customWidth="1"/>
+    <col min="36" max="36" width="11.81640625" customWidth="1"/>
     <col min="37" max="37" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>6</v>
       </c>
@@ -2468,7 +1850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
         <v>48</v>
       </c>
@@ -2500,7 +1882,6 @@
         <v>55</v>
       </c>
       <c r="M2" s="20">
-        <f>[1]prod_table_raw!N13</f>
         <v>166000</v>
       </c>
       <c r="N2">
@@ -2512,7 +1893,6 @@
         <v>165999.07959030612</v>
       </c>
       <c r="Q2" s="2">
-        <f>[1]prod_table_raw!N14</f>
         <v>0.90200150000000001</v>
       </c>
       <c r="R2" s="2"/>
@@ -2528,23 +1908,18 @@
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2">
-        <f>S2/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE2">
-        <f>T2/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF2">
-        <f>V2/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG2">
-        <f>W2/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH2">
-        <f>X2/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI2" s="2"/>
@@ -2555,7 +1930,7 @@
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>56</v>
       </c>
@@ -2587,7 +1962,6 @@
         <v>55</v>
       </c>
       <c r="M3" s="20">
-        <f>[1]prod_table_raw!N17</f>
         <v>17332900</v>
       </c>
       <c r="N3">
@@ -2599,11 +1973,9 @@
         <v>17332870.960915469</v>
       </c>
       <c r="Q3" s="2">
-        <f>[1]prod_table_raw!N18</f>
         <v>18.785114342499998</v>
       </c>
       <c r="R3" s="2">
-        <f>[1]prod_table_raw!N19</f>
         <v>9.6731885000000002</v>
       </c>
       <c r="S3" s="2"/>
@@ -2618,23 +1990,18 @@
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3">
-        <f>S3/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f>T3/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>V3/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>W3/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>X3/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI3" s="2"/>
@@ -2645,7 +2012,7 @@
         <v>29.039084533163262</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
         <v>61</v>
       </c>
@@ -2677,7 +2044,6 @@
         <v>55</v>
       </c>
       <c r="M4" s="20">
-        <f>[1]prod_table_raw!N24</f>
         <v>1361450</v>
       </c>
       <c r="N4">
@@ -2689,11 +2055,9 @@
         <v>1361446.483400204</v>
       </c>
       <c r="Q4" s="2">
-        <f>[1]prod_table_raw!N22</f>
         <v>2.6935630999999902</v>
       </c>
       <c r="R4" s="2">
-        <f>[1]prod_table_raw!N23</f>
         <v>0.7527047</v>
       </c>
       <c r="S4" s="2"/>
@@ -2708,23 +2072,18 @@
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
       <c r="AD4">
-        <f>S4/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>T4/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>V4/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>W4/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>X4/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI4" s="2"/>
@@ -2735,7 +2094,7 @@
         <v>3.5165997959183577</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>68</v>
       </c>
@@ -2767,11 +2126,9 @@
         <v>73</v>
       </c>
       <c r="M5" s="20">
-        <f>[1]prod_table_raw!N36</f>
         <v>6862152</v>
       </c>
       <c r="O5">
-        <f>S5/([1]concentrate_grade!$F$4/100)</f>
         <v>63500</v>
       </c>
       <c r="P5">
@@ -2779,15 +2136,12 @@
         <v>6798652</v>
       </c>
       <c r="Q5" s="2">
-        <f>[1]prod_table_raw!N35</f>
         <v>0.27520376799999902</v>
       </c>
       <c r="R5" s="2">
-        <f>[1]prod_table_raw!N38</f>
         <v>6.7893341869999997</v>
       </c>
       <c r="S5" s="2">
-        <f>[1]prod_table_raw!N39</f>
         <v>19050</v>
       </c>
       <c r="T5" s="2"/>
@@ -2801,23 +2155,18 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5">
-        <f>S5/([1]concentrate_grade!$F$4/100)</f>
         <v>63500</v>
       </c>
       <c r="AE5">
-        <f>T5/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>V5/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>W5/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>X5/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="2"/>
@@ -2828,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>74</v>
       </c>
@@ -2860,7 +2209,6 @@
         <v>55</v>
       </c>
       <c r="M6" s="20">
-        <f>[1]prod_table_raw!N48</f>
         <v>25434853.502416398</v>
       </c>
       <c r="N6">
@@ -2872,11 +2220,9 @@
         <v>25434829.49413256</v>
       </c>
       <c r="Q6" s="2">
-        <f>[1]prod_table_raw!N49</f>
         <v>21.070941660999999</v>
       </c>
       <c r="R6" s="2">
-        <f>[1]prod_table_raw!N50</f>
         <v>2.4571765000000001</v>
       </c>
       <c r="S6" s="2"/>
@@ -2891,23 +2237,18 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6">
-        <f>S6/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>T6/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>V6/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>W6/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>X6/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI6" s="2"/>
@@ -2918,7 +2259,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
         <v>77</v>
       </c>
@@ -2950,7 +2291,6 @@
         <v>55</v>
       </c>
       <c r="M7" s="20">
-        <f>[1]prod_table_raw!N55</f>
         <v>222627</v>
       </c>
       <c r="N7">
@@ -2962,7 +2302,6 @@
         <v>222624.22394914847</v>
       </c>
       <c r="Q7" s="2">
-        <f>[1]prod_table_raw!N54</f>
         <v>2.7205298345000002</v>
       </c>
       <c r="R7" s="2"/>
@@ -2978,23 +2317,18 @@
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
       <c r="AD7">
-        <f>S7/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>T7/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>V7/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>W7/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>X7/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI7" s="2"/>
@@ -3005,7 +2339,7 @@
         <v>2.7760508515306124</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
         <v>79</v>
       </c>
@@ -3037,7 +2371,6 @@
         <v>55</v>
       </c>
       <c r="M8" s="20">
-        <f>[1]prod_table_raw!N62</f>
         <v>1661000</v>
       </c>
       <c r="N8">
@@ -3049,11 +2382,9 @@
         <v>1660992.2611000792</v>
       </c>
       <c r="Q8" s="2">
-        <f>[1]prod_table_raw!N59</f>
         <v>7.2160120000000001</v>
       </c>
       <c r="R8" s="2">
-        <f>[1]prod_table_raw!N60</f>
         <v>0.36810992249999902</v>
       </c>
       <c r="S8" s="2"/>
@@ -3068,23 +2399,18 @@
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8">
-        <f>S8/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f>T8/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f>V8/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f>W8/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f>X8/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI8" s="2"/>
@@ -3095,7 +2421,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
         <v>82</v>
       </c>
@@ -3127,11 +2453,9 @@
         <v>87</v>
       </c>
       <c r="M9" s="20">
-        <f>[1]prod_table_raw!N80</f>
         <v>30000000</v>
       </c>
       <c r="O9">
-        <f>S9/([1]concentrate_grade!$F$4/100)+V9/([1]concentrate_grade!$F$5/100)</f>
         <v>186436.98475294118</v>
       </c>
       <c r="P9">
@@ -3141,13 +2465,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2">
-        <f>[1]prod_table_raw!N82</f>
         <v>55610.379200000003</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2">
-        <f>[1]prod_table_raw!N81</f>
         <v>545.21758399999999</v>
       </c>
       <c r="W9" s="2"/>
@@ -3158,23 +2480,18 @@
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
       <c r="AD9">
-        <f>S9/([1]concentrate_grade!$F$4/100)</f>
         <v>185367.93066666668</v>
       </c>
       <c r="AE9">
-        <f>T9/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>V9/([1]concentrate_grade!$F$5/100)</f>
         <v>1069.0540862745097</v>
       </c>
       <c r="AG9">
-        <f>W9/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>X9/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI9" s="2"/>
@@ -3185,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
         <v>88</v>
       </c>
@@ -3217,7 +2534,6 @@
         <v>92</v>
       </c>
       <c r="M10" s="20">
-        <f>[1]prod_table_raw!N86</f>
         <v>2886927.3287240001</v>
       </c>
       <c r="N10">
@@ -3225,7 +2541,6 @@
         <v>4.4745421183166938</v>
       </c>
       <c r="O10">
-        <f>S10/([1]concentrate_grade!$F$4/100)</f>
         <v>130.12252666666666</v>
       </c>
       <c r="P10">
@@ -3233,12 +2548,10 @@
         <v>2886792.7316552154</v>
       </c>
       <c r="Q10" s="2">
-        <f>[1]prod_table_raw!N87</f>
         <v>4.3850512759503602</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" s="2">
-        <f>[1]prod_table_raw!N85</f>
         <v>39.036757999999999</v>
       </c>
       <c r="T10" s="2"/>
@@ -3252,23 +2565,18 @@
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
       <c r="AD10">
-        <f>S10/([1]concentrate_grade!$F$4/100)</f>
         <v>130.12252666666666</v>
       </c>
       <c r="AE10">
-        <f>T10/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF10">
-        <f>V10/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG10">
-        <f>W10/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH10">
-        <f>X10/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI10" s="2"/>
@@ -3279,7 +2587,7 @@
         <v>4.4745421183166938</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
         <v>93</v>
       </c>
@@ -3311,7 +2619,6 @@
         <v>55</v>
       </c>
       <c r="M11" s="20">
-        <f>[1]prod_table_raw!N91</f>
         <v>1266009</v>
       </c>
       <c r="N11">
@@ -3323,7 +2630,6 @@
         <v>1266004.5234763699</v>
       </c>
       <c r="Q11" s="2">
-        <f>[1]prod_table_raw!N92</f>
         <v>4.3869931575000001</v>
       </c>
       <c r="R11" s="2"/>
@@ -3339,23 +2645,18 @@
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
       <c r="AD11">
-        <f>S11/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE11">
-        <f>T11/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF11">
-        <f>V11/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG11">
-        <f>W11/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH11">
-        <f>X11/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI11" s="2"/>
@@ -3366,7 +2667,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
         <v>95</v>
       </c>
@@ -3398,11 +2699,9 @@
         <v>87</v>
       </c>
       <c r="M12" s="20">
-        <f>[1]prod_table_raw!N93</f>
         <v>17408000</v>
       </c>
       <c r="O12">
-        <f>S12/([1]concentrate_grade!$F$4/100)+V12/([1]concentrate_grade!$F$5/100)</f>
         <v>343098.03921568632</v>
       </c>
       <c r="P12">
@@ -3412,13 +2711,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2">
-        <f>[1]prod_table_raw!N95</f>
         <v>102400</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2">
-        <f>[1]prod_table_raw!N94</f>
         <v>900</v>
       </c>
       <c r="W12" s="2"/>
@@ -3429,23 +2726,18 @@
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
       <c r="AD12">
-        <f>S12/([1]concentrate_grade!$F$4/100)</f>
         <v>341333.33333333337</v>
       </c>
       <c r="AE12">
-        <f>T12/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF12">
-        <f>V12/([1]concentrate_grade!$F$5/100)</f>
         <v>1764.7058823529412</v>
       </c>
       <c r="AG12">
-        <f>W12/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH12">
-        <f>X12/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI12" s="2"/>
@@ -3456,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
         <v>98</v>
       </c>
@@ -3488,7 +2780,6 @@
         <v>55</v>
       </c>
       <c r="M13" s="20">
-        <f>[1]prod_table_raw!N105</f>
         <v>439008</v>
       </c>
       <c r="N13">
@@ -3500,7 +2791,6 @@
         <v>439003.82959193876</v>
       </c>
       <c r="Q13" s="2">
-        <f>[1]prod_table_raw!N103</f>
         <v>4.0869999000000004</v>
       </c>
       <c r="R13" s="2"/>
@@ -3516,23 +2806,18 @@
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13">
-        <f>S13/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>T13/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>V13/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>W13/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f>X13/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI13" s="2"/>
@@ -3543,7 +2828,7 @@
         <v>4.1704080612244905</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
         <v>102</v>
       </c>
@@ -3575,11 +2860,9 @@
         <v>106</v>
       </c>
       <c r="M14" s="20">
-        <f>[1]prod_table_raw!N116</f>
         <v>1340000</v>
       </c>
       <c r="O14">
-        <f>S14/([1]concentrate_grade!$F$4/100)+W14/([1]concentrate_grade!$F$9/100)</f>
         <v>152533.33333333334</v>
       </c>
       <c r="P14">
@@ -3588,18 +2871,15 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2">
-        <f>[1]prod_table_raw!N115</f>
         <v>42.860622999999997</v>
       </c>
       <c r="S14" s="2">
-        <f>[1]prod_table_raw!N113</f>
         <v>22600</v>
       </c>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2">
-        <f>[1]prod_table_raw!N114</f>
         <v>38600</v>
       </c>
       <c r="X14" s="2"/>
@@ -3609,23 +2889,18 @@
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
       <c r="AD14">
-        <f>S14/([1]concentrate_grade!$F$4/100)</f>
         <v>75333.333333333343</v>
       </c>
       <c r="AE14">
-        <f>T14/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF14">
-        <f>V14/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG14">
-        <f>W14/([1]concentrate_grade!$F$9/100)</f>
         <v>77200</v>
       </c>
       <c r="AH14">
-        <f>X14/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI14" s="2"/>
@@ -3636,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
         <v>107</v>
       </c>
@@ -3668,7 +2943,6 @@
         <v>55</v>
       </c>
       <c r="M15" s="20">
-        <f>[1]prod_table_raw!N120</f>
         <v>191148</v>
       </c>
       <c r="N15">
@@ -3680,11 +2954,9 @@
         <v>191146.77982239029</v>
       </c>
       <c r="Q15" s="2">
-        <f>[1]prod_table_raw!N119</f>
         <v>1.1053250795</v>
       </c>
       <c r="R15" s="2">
-        <f>[1]prod_table_raw!N121</f>
         <v>9.0448977999999999E-2</v>
       </c>
       <c r="S15" s="2"/>
@@ -3699,23 +2971,18 @@
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
       <c r="AD15">
-        <f>S15/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE15">
-        <f>T15/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF15">
-        <f>V15/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG15">
-        <f>W15/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH15">
-        <f>X15/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI15" s="2"/>
@@ -3726,7 +2993,7 @@
         <v>1.2201776096938775</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
         <v>110</v>
       </c>
@@ -3758,7 +3025,6 @@
         <v>114</v>
       </c>
       <c r="M16" s="20">
-        <f>[1]prod_table_raw!N139</f>
         <v>1501500</v>
       </c>
       <c r="N16">
@@ -3766,7 +3032,6 @@
         <v>9.8029027903061134</v>
       </c>
       <c r="O16">
-        <f>S16/([1]concentrate_grade!$F$4/100)+W16/([1]concentrate_grade!$F$9/100)</f>
         <v>23998.078283999999</v>
       </c>
       <c r="P16">
@@ -3774,22 +3039,18 @@
         <v>1477492.1188132097</v>
       </c>
       <c r="Q16" s="2">
-        <f>[1]prod_table_raw!N138</f>
         <v>7.3401460684999904</v>
       </c>
       <c r="R16" s="2">
-        <f>[1]prod_table_raw!N135</f>
         <v>2.2666986659999999</v>
       </c>
       <c r="S16" s="2">
-        <f>[1]prod_table_raw!N137</f>
         <v>2577.9603750000001</v>
       </c>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2">
-        <f>[1]prod_table_raw!N136</f>
         <v>7702.4385169999996</v>
       </c>
       <c r="X16" s="2"/>
@@ -3799,23 +3060,18 @@
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
       <c r="AD16">
-        <f>S16/([1]concentrate_grade!$F$4/100)</f>
         <v>8593.2012500000001</v>
       </c>
       <c r="AE16">
-        <f>T16/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF16">
-        <f>V16/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG16">
-        <f>W16/([1]concentrate_grade!$F$9/100)</f>
         <v>15404.877033999999</v>
       </c>
       <c r="AH16">
-        <f>X16/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI16" s="2"/>
@@ -3826,7 +3082,7 @@
         <v>9.8029027903061134</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
         <v>115</v>
       </c>
@@ -3858,7 +3114,6 @@
         <v>55</v>
       </c>
       <c r="M17" s="20">
-        <f>[1]prod_table_raw!N146</f>
         <v>441588</v>
       </c>
       <c r="N17">
@@ -3870,7 +3125,6 @@
         <v>441580.74669553828</v>
       </c>
       <c r="Q17" s="2">
-        <f>[1]prod_table_raw!N147</f>
         <v>7.1082383724999998</v>
       </c>
       <c r="R17" s="2"/>
@@ -3886,23 +3140,18 @@
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17">
-        <f>S17/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE17">
-        <f>T17/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF17">
-        <f>V17/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG17">
-        <f>W17/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH17">
-        <f>X17/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI17" s="2"/>
@@ -3913,7 +3162,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>117</v>
       </c>
@@ -3945,7 +3194,6 @@
         <v>55</v>
       </c>
       <c r="M18" s="20">
-        <f>[1]prod_table_raw!N150</f>
         <v>1165551</v>
       </c>
       <c r="N18">
@@ -3957,7 +3205,6 @@
         <v>1165549.9526372449</v>
       </c>
       <c r="Q18" s="2">
-        <f>[1]prod_table_raw!N148</f>
         <v>1.0264154999999999</v>
       </c>
       <c r="R18" s="2"/>
@@ -3973,23 +3220,18 @@
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
       <c r="AD18">
-        <f>S18/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE18">
-        <f>T18/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF18">
-        <f>V18/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG18">
-        <f>W18/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH18">
-        <f>X18/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI18" s="2"/>
@@ -4000,7 +3242,7 @@
         <v>1.0473627551020408</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>120</v>
       </c>
@@ -4032,7 +3274,6 @@
         <v>55</v>
       </c>
       <c r="M19" s="20">
-        <f>[1]prod_table_raw!N163</f>
         <v>1918143</v>
       </c>
       <c r="N19">
@@ -4044,11 +3285,9 @@
         <v>1918130.58586317</v>
       </c>
       <c r="Q19" s="2">
-        <f>[1]prod_table_raw!N164</f>
         <v>11.326059593499901</v>
       </c>
       <c r="R19" s="2">
-        <f>[1]prod_table_raw!N165</f>
         <v>0.8397945</v>
       </c>
       <c r="S19" s="2"/>
@@ -4063,23 +3302,18 @@
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
       <c r="AD19">
-        <f>S19/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE19">
-        <f>T19/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF19">
-        <f>V19/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG19">
-        <f>W19/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH19">
-        <f>X19/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI19" s="2"/>
@@ -4090,7 +3324,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
         <v>122</v>
       </c>
@@ -4122,11 +3356,9 @@
         <v>73</v>
       </c>
       <c r="M20" s="20">
-        <f>[1]prod_table_raw!N175</f>
         <v>21680000</v>
       </c>
       <c r="O20">
-        <f>S20/([1]concentrate_grade!$F$4/100)</f>
         <v>93533.694346666671</v>
       </c>
       <c r="P20">
@@ -4134,12 +3366,10 @@
         <v>21586466.305653334</v>
       </c>
       <c r="Q20" s="2">
-        <f>[1]prod_table_raw!N173</f>
         <v>4.8021004684999999</v>
       </c>
       <c r="R20" s="2"/>
       <c r="S20" s="2">
-        <f>[1]prod_table_raw!N171</f>
         <v>28060.108304000001</v>
       </c>
       <c r="T20" s="2"/>
@@ -4153,23 +3383,18 @@
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20">
-        <f>S20/([1]concentrate_grade!$F$4/100)</f>
         <v>93533.694346666671</v>
       </c>
       <c r="AE20">
-        <f>T20/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF20">
-        <f>V20/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG20">
-        <f>W20/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH20">
-        <f>X20/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI20" s="2"/>
@@ -4180,7 +3405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
         <v>125</v>
       </c>
@@ -4212,11 +3437,9 @@
         <v>73</v>
       </c>
       <c r="M21" s="20">
-        <f>[1]prod_table_raw!N179</f>
         <v>5948239</v>
       </c>
       <c r="O21">
-        <f>S21/([1]concentrate_grade!$F$4/100)</f>
         <v>45578.436133333336</v>
       </c>
       <c r="P21">
@@ -4224,12 +3447,10 @@
         <v>5902660.5638666665</v>
       </c>
       <c r="Q21" s="2">
-        <f>[1]prod_table_raw!N178</f>
         <v>1.301183819</v>
       </c>
       <c r="R21" s="2"/>
       <c r="S21" s="2">
-        <f>[1]prod_table_raw!N180</f>
         <v>13673.530839999999</v>
       </c>
       <c r="T21" s="2"/>
@@ -4243,23 +3464,18 @@
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
       <c r="AD21">
-        <f>S21/([1]concentrate_grade!$F$4/100)</f>
         <v>45578.436133333336</v>
       </c>
       <c r="AE21">
-        <f>T21/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF21">
-        <f>V21/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG21">
-        <f>W21/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH21">
-        <f>X21/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI21" s="2"/>
@@ -4270,7 +3486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
         <v>128</v>
       </c>
@@ -4302,7 +3518,6 @@
         <v>55</v>
       </c>
       <c r="M22" s="20">
-        <f>[1]prod_table_raw!N183</f>
         <v>1028000</v>
       </c>
       <c r="N22">
@@ -4314,7 +3529,6 @@
         <v>1027994.2871122449</v>
       </c>
       <c r="Q22" s="2">
-        <f>[1]prod_table_raw!N184</f>
         <v>5.59863</v>
       </c>
       <c r="R22" s="2"/>
@@ -4330,23 +3544,18 @@
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
       <c r="AD22">
-        <f>S22/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE22">
-        <f>T22/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF22">
-        <f>V22/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG22">
-        <f>W22/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH22">
-        <f>X22/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI22" s="2"/>
@@ -4357,7 +3566,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
         <v>130</v>
       </c>
@@ -4389,11 +3598,9 @@
         <v>73</v>
       </c>
       <c r="M23" s="20">
-        <f>[1]prod_table_raw!N189</f>
         <v>3065000</v>
       </c>
       <c r="O23">
-        <f>S23/([1]concentrate_grade!$F$4/100)</f>
         <v>71667.536000000007</v>
       </c>
       <c r="P23">
@@ -4401,12 +3608,10 @@
         <v>2993332.4640000002</v>
       </c>
       <c r="Q23" s="2">
-        <f>[1]prod_table_raw!N187</f>
         <v>2.0974023155000001</v>
       </c>
       <c r="R23" s="2"/>
       <c r="S23" s="2">
-        <f>[1]prod_table_raw!N190</f>
         <v>21500.2608</v>
       </c>
       <c r="T23" s="2"/>
@@ -4420,23 +3625,18 @@
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
       <c r="AD23">
-        <f>S23/([1]concentrate_grade!$F$4/100)</f>
         <v>71667.536000000007</v>
       </c>
       <c r="AE23">
-        <f>T23/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF23">
-        <f>V23/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG23">
-        <f>W23/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH23">
-        <f>X23/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI23" s="2"/>
@@ -4447,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
         <v>132</v>
       </c>
@@ -4479,11 +3679,9 @@
         <v>67</v>
       </c>
       <c r="M24" s="20">
-        <f>[1]prod_table_raw!N202</f>
         <v>6835294.1176470499</v>
       </c>
       <c r="O24">
-        <f>T24/([1]concentrate_grade!$F$6/100)</f>
         <v>363125</v>
       </c>
       <c r="P24">
@@ -4493,11 +3691,9 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2">
-        <f>[1]prod_table_raw!N200</f>
         <v>40926</v>
       </c>
       <c r="T24" s="2">
-        <f>[1]prod_table_raw!N201</f>
         <v>58100</v>
       </c>
       <c r="U24" s="2"/>
@@ -4510,19 +3706,15 @@
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
       <c r="AE24">
-        <f>T24/([1]concentrate_grade!$F$6/100)</f>
         <v>363125</v>
       </c>
       <c r="AF24">
-        <f>V24/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG24">
-        <f>W24/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH24">
-        <f>X24/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI24" s="2"/>
@@ -4533,7 +3725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
         <v>135</v>
       </c>
@@ -4565,11 +3757,9 @@
         <v>67</v>
       </c>
       <c r="M25" s="20">
-        <f>[1]prod_table_raw!N207</f>
         <v>1500000</v>
       </c>
       <c r="O25">
-        <f>T25/([1]concentrate_grade!$F$6/100)</f>
         <v>151450</v>
       </c>
       <c r="P25">
@@ -4579,15 +3769,12 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2">
-        <f>[1]prod_table_raw!N203</f>
         <v>5488</v>
       </c>
       <c r="T25" s="2">
-        <f>[1]prod_table_raw!N204</f>
         <v>24232</v>
       </c>
       <c r="U25" s="2">
-        <f>[1]prod_table_raw!N205</f>
         <v>498</v>
       </c>
       <c r="V25" s="2"/>
@@ -4595,26 +3782,21 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2">
-        <f>[1]prod_table_raw!N206</f>
         <v>4.4160749299999997</v>
       </c>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
       <c r="AE25">
-        <f>T25/([1]concentrate_grade!$F$6/100)</f>
         <v>151450</v>
       </c>
       <c r="AF25">
-        <f>V25/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG25">
-        <f>W25/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH25">
-        <f>X25/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI25" s="2"/>
@@ -4625,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
         <v>139</v>
       </c>
@@ -4657,7 +3839,6 @@
         <v>55</v>
       </c>
       <c r="M26" s="20">
-        <f>[1]prod_table_raw!N211</f>
         <v>8764000</v>
       </c>
       <c r="N26">
@@ -4669,7 +3850,6 @@
         <v>8763991.9465738703</v>
       </c>
       <c r="Q26" s="2">
-        <f>[1]prod_table_raw!N212</f>
         <v>7.8923576074999904</v>
       </c>
       <c r="R26" s="2"/>
@@ -4685,23 +3865,18 @@
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26">
-        <f>S26/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE26">
-        <f>T26/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF26">
-        <f>V26/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG26">
-        <f>W26/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH26">
-        <f>X26/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI26" s="2"/>
@@ -4712,12 +3887,12 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" t="s">
         <v>283</v>
-      </c>
-      <c r="C27" t="s">
-        <v>284</v>
       </c>
       <c r="E27" t="s">
         <v>64</v>
@@ -4729,7 +3904,7 @@
         <v>51</v>
       </c>
       <c r="H27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I27" s="21" t="s">
         <v>53</v>
@@ -4772,7 +3947,7 @@
       <c r="AJ27" s="2"/>
       <c r="AK27" s="2"/>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
         <v>141</v>
       </c>
@@ -4804,11 +3979,9 @@
         <v>67</v>
       </c>
       <c r="M28" s="20">
-        <f>[1]prod_table_raw!N250</f>
         <v>464705.88235294097</v>
       </c>
       <c r="O28">
-        <f>T28/([1]concentrate_grade!$F$6/100)</f>
         <v>49375</v>
       </c>
       <c r="P28">
@@ -4818,11 +3991,9 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2">
-        <f>[1]prod_table_raw!N248</f>
         <v>4700</v>
       </c>
       <c r="T28" s="2">
-        <f>[1]prod_table_raw!N249</f>
         <v>7900</v>
       </c>
       <c r="U28" s="2"/>
@@ -4835,19 +4006,15 @@
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
       <c r="AE28">
-        <f>T28/([1]concentrate_grade!$F$6/100)</f>
         <v>49375</v>
       </c>
       <c r="AF28">
-        <f>V28/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG28">
-        <f>W28/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH28">
-        <f>X28/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI28" s="2"/>
@@ -4858,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
         <v>145</v>
       </c>
@@ -4890,11 +4057,9 @@
         <v>67</v>
       </c>
       <c r="M29" s="20">
-        <f>[1]prod_table_raw!N268</f>
         <v>794117.64705882303</v>
       </c>
       <c r="O29">
-        <f>T29/([1]concentrate_grade!$F$6/100)</f>
         <v>84375</v>
       </c>
       <c r="P29">
@@ -4904,11 +4069,9 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
       <c r="S29" s="2">
-        <f>[1]prod_table_raw!N266</f>
         <v>9600</v>
       </c>
       <c r="T29" s="2">
-        <f>[1]prod_table_raw!N267</f>
         <v>13500</v>
       </c>
       <c r="U29" s="2"/>
@@ -4921,19 +4084,15 @@
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
       <c r="AE29">
-        <f>T29/([1]concentrate_grade!$F$6/100)</f>
         <v>84375</v>
       </c>
       <c r="AF29">
-        <f>V29/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG29">
-        <f>W29/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH29">
-        <f>X29/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI29" s="2"/>
@@ -4944,7 +4103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
         <v>148</v>
       </c>
@@ -4976,7 +4135,6 @@
         <v>55</v>
       </c>
       <c r="M30" s="20">
-        <f>[1]prod_table_raw!N271</f>
         <v>1034000</v>
       </c>
       <c r="N30">
@@ -4988,11 +4146,9 @@
         <v>1033995.8818331235</v>
       </c>
       <c r="Q30" s="2">
-        <f>[1]prod_table_raw!N273</f>
         <v>2.8926254999999998</v>
       </c>
       <c r="R30" s="2">
-        <f>[1]prod_table_raw!N274</f>
         <v>1.1431780389999999</v>
       </c>
       <c r="S30" s="2"/>
@@ -5007,23 +4163,18 @@
       <c r="AB30" s="2"/>
       <c r="AC30" s="2"/>
       <c r="AD30">
-        <f>S30/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE30">
-        <f>T30/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF30">
-        <f>V30/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG30">
-        <f>W30/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH30">
-        <f>X30/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI30" s="2"/>
@@ -5034,7 +4185,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
         <v>150</v>
       </c>
@@ -5066,7 +4217,6 @@
         <v>55</v>
       </c>
       <c r="M31" s="20">
-        <f>[1]prod_table_raw!N277</f>
         <v>2878047</v>
       </c>
       <c r="N31">
@@ -5078,7 +4228,6 @@
         <v>2878041.125247092</v>
       </c>
       <c r="Q31" s="2">
-        <f>[1]prod_table_raw!N275</f>
         <v>5.7572578499999896</v>
       </c>
       <c r="R31" s="2"/>
@@ -5094,23 +4243,18 @@
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
       <c r="AD31">
-        <f>S31/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE31">
-        <f>T31/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF31">
-        <f>V31/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG31">
-        <f>W31/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH31">
-        <f>X31/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI31" s="2"/>
@@ -5121,7 +4265,7 @@
         <v>5.8747529081632548</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" s="20"/>
       <c r="B32" t="s">
         <v>152</v>
@@ -5154,7 +4298,6 @@
         <v>157</v>
       </c>
       <c r="M32" s="20">
-        <f>[1]prod_table_raw!N154</f>
         <v>43726.856187782003</v>
       </c>
       <c r="O32" s="2">
@@ -5177,34 +4320,27 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
       <c r="AB32" s="2">
-        <f>[1]prod_table_raw!N155</f>
         <v>8164.6559999999999</v>
       </c>
       <c r="AC32" s="2"/>
       <c r="AD32">
-        <f>S32/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE32">
-        <f>T32/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF32">
-        <f>V32/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG32">
-        <f>W32/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH32">
-        <f>X32/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI32" s="2"/>
       <c r="AJ32" s="2"/>
       <c r="AK32" s="2">
-        <f>AB32/([1]concentrate_grade!$F$10/100)</f>
         <v>9605.477647058824</v>
       </c>
       <c r="AL32">
@@ -5212,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A33" s="20"/>
       <c r="B33" t="s">
         <v>158</v>
@@ -5245,7 +4381,6 @@
         <v>157</v>
       </c>
       <c r="M33" s="20">
-        <f>[1]prod_table_raw!N153</f>
         <v>98408.871032543204</v>
       </c>
       <c r="O33" s="2">
@@ -5268,34 +4403,27 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
       <c r="AB33" s="2">
-        <f>[1]prod_table_raw!N152</f>
         <v>6123.4920000000002</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33">
-        <f>S33/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE33">
-        <f>T33/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF33">
-        <f>V33/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG33">
-        <f>W33/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH33">
-        <f>X33/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI33" s="2"/>
       <c r="AJ33" s="2"/>
       <c r="AK33" s="2">
-        <f>AB33/([1]concentrate_grade!$F$10/100)</f>
         <v>7204.1082352941185</v>
       </c>
       <c r="AL33">
@@ -5303,7 +4431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34" s="20"/>
       <c r="B34" t="s">
         <v>159</v>
@@ -5336,7 +4464,6 @@
         <v>55</v>
       </c>
       <c r="M34" s="20">
-        <f>[1]prod_table_raw!N160</f>
         <v>3842649.0057279998</v>
       </c>
       <c r="N34">
@@ -5348,11 +4475,9 @@
         <v>3842631.3381266426</v>
       </c>
       <c r="Q34" s="2">
-        <f>[1]prod_table_raw!N161</f>
         <v>13.426311830047601</v>
       </c>
       <c r="R34" s="2">
-        <f>[1]prod_table_raw!N162</f>
         <v>3.8879375</v>
       </c>
       <c r="S34" s="2"/>
@@ -5367,23 +4492,18 @@
       <c r="AB34" s="2"/>
       <c r="AC34" s="2"/>
       <c r="AD34">
-        <f>S34/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE34">
-        <f>T34/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF34">
-        <f>V34/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG34">
-        <f>W34/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH34">
-        <f>X34/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI34" s="2"/>
@@ -5394,7 +4514,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A35" s="20"/>
       <c r="B35" t="s">
         <v>162</v>
@@ -5427,7 +4547,6 @@
         <v>55</v>
       </c>
       <c r="M35" s="20">
-        <f>[1]prod_table_raw!N101</f>
         <v>2911000</v>
       </c>
       <c r="N35">
@@ -5439,7 +4558,6 @@
         <v>2910991.7480510203</v>
       </c>
       <c r="Q35" s="2">
-        <f>[1]prod_table_raw!N100</f>
         <v>8.0869099999999996</v>
       </c>
       <c r="R35" s="2"/>
@@ -5455,23 +4573,18 @@
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
       <c r="AD35">
-        <f>S35/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE35">
-        <f>T35/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF35">
-        <f>V35/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG35">
-        <f>W35/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH35">
-        <f>X35/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI35" s="2"/>
@@ -5482,7 +4595,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A36" s="20"/>
       <c r="B36" t="s">
         <v>164</v>
@@ -5515,7 +4628,6 @@
         <v>55</v>
       </c>
       <c r="M36" s="20">
-        <f>[1]prod_table_raw!N254</f>
         <v>1574000</v>
       </c>
       <c r="N36">
@@ -5527,7 +4639,6 @@
         <v>1573995.7819845409</v>
       </c>
       <c r="Q36" s="2">
-        <f>[1]prod_table_raw!N255</f>
         <v>4.1336551500000001</v>
       </c>
       <c r="R36" s="2"/>
@@ -5543,23 +4654,18 @@
       <c r="AB36" s="2"/>
       <c r="AC36" s="2"/>
       <c r="AD36">
-        <f>S36/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE36">
-        <f>T36/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF36">
-        <f>V36/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG36">
-        <f>W36/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH36">
-        <f>X36/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI36" s="2"/>
@@ -5570,7 +4676,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A37" s="20"/>
       <c r="B37" t="s">
         <v>166</v>
@@ -5603,7 +4709,6 @@
         <v>55</v>
       </c>
       <c r="M37" s="20">
-        <f>[1]prod_table_raw!N229</f>
         <v>122000</v>
       </c>
       <c r="N37">
@@ -5615,7 +4720,6 @@
         <v>121998.76992005153</v>
       </c>
       <c r="Q37" s="2">
-        <f>[1]prod_table_raw!N231</f>
         <v>1.2054783495000001</v>
       </c>
       <c r="R37" s="2"/>
@@ -5631,23 +4735,18 @@
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
       <c r="AD37">
-        <f>S37/([1]concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
       <c r="AE37">
-        <f>T37/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF37">
-        <f>V37/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG37">
-        <f>W37/([1]concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
       <c r="AH37">
-        <f>X37/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI37" s="2"/>
@@ -5658,7 +4757,7 @@
         <v>1.2300799484693878</v>
       </c>
     </row>
-    <row r="38" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="22"/>
       <c r="B38" s="23" t="s">
         <v>168</v>
@@ -5692,7 +4791,6 @@
         <v>114</v>
       </c>
       <c r="M38" s="22">
-        <f>[1]prod_table_raw!N193+[1]prod_table_raw!N130</f>
         <v>2123641</v>
       </c>
       <c r="N38">
@@ -5700,7 +4798,6 @@
         <v>32.978787143877547</v>
       </c>
       <c r="O38">
-        <f>S38/([1]concentrate_grade!$F$4/100)+W38/([1]concentrate_grade!$F$9/100)</f>
         <v>109797.33333333334</v>
       </c>
       <c r="P38">
@@ -5708,22 +4805,18 @@
         <v>2013810.687879523</v>
       </c>
       <c r="Q38" s="25">
-        <f>[1]prod_table_raw!N232</f>
         <v>5.8276450705</v>
       </c>
       <c r="R38" s="25">
-        <f>[1]prod_table_raw!N233</f>
         <v>26.4915663305</v>
       </c>
       <c r="S38" s="25">
-        <f>[1]prod_table_raw!N235</f>
         <v>12154</v>
       </c>
       <c r="T38" s="25"/>
       <c r="U38" s="25"/>
       <c r="V38" s="25"/>
       <c r="W38" s="25">
-        <f>[1]prod_table_raw!N234</f>
         <v>34642</v>
       </c>
       <c r="X38" s="25"/>
@@ -5733,23 +4826,18 @@
       <c r="AB38" s="25"/>
       <c r="AC38" s="25"/>
       <c r="AD38">
-        <f>S38/([1]concentrate_grade!$F$4/100)</f>
         <v>40513.333333333336</v>
       </c>
       <c r="AE38">
-        <f>T38/([1]concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
       <c r="AF38">
-        <f>V38/([1]concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
       <c r="AG38">
-        <f>W38/([1]concentrate_grade!$F$9/100)</f>
         <v>69284</v>
       </c>
       <c r="AH38">
-        <f>X38/([1]concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
       <c r="AI38" s="25"/>
@@ -5760,8 +4848,8 @@
         <v>32.978787143877547</v>
       </c>
     </row>
-    <row r="39" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M40" s="26">
         <f>SUM(M2:M38)</f>
         <v>177146686.21114755</v>
@@ -5870,44 +4958,43 @@
   </sheetData>
   <autoFilter ref="A1:DR38" xr:uid="{B231D443-D3C4-4EF0-BDC9-8F5B03D7CAA5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130C853C-0E0A-459D-8C54-D8929ADDDD8D}">
   <dimension ref="A1:F47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
@@ -5922,14 +5009,14 @@
         <v>BC-MAIN-857b7b89</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F2" s="5">
         <f>market_shares_calc!E2</f>
         <v>4.4998730921635586E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
@@ -5944,14 +5031,14 @@
         <v>QC-MAIN-e7e6a960</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F3" s="5">
         <f>market_shares_calc!E3</f>
         <v>0.14197177189794855</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -5966,19 +5053,19 @@
         <v>QC-MAIN-b86f7d07</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F4" s="5">
         <f>market_shares_calc!E4</f>
         <v>1.7192618572817963E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>153</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>153</v>
@@ -5988,19 +5075,19 @@
         <v>GRP-91aaa60b</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F5" s="5">
         <f>market_shares_calc!H32</f>
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>69</v>
@@ -6010,14 +5097,14 @@
         <v>BC-MAIN-599152a0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F6" s="6">
         <f>market_shares_calc!F5</f>
         <v>6.8607786524216438E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
@@ -6032,14 +5119,14 @@
         <v>ON-MAIN-aeafbb59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F7" s="5">
         <f>market_shares_calc!E6</f>
         <v>0.11737624141637086</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>78</v>
       </c>
@@ -6054,14 +5141,14 @@
         <v>ON-MAIN-cb85213a</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F8" s="5">
         <f>market_shares_calc!E7</f>
         <v>1.3572082750078275E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>80</v>
       </c>
@@ -6076,19 +5163,19 @@
         <v>QC-MAIN-6dc537e6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F9" s="5">
         <f>market_shares_calc!E8</f>
         <v>3.7835398463024174E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>83</v>
@@ -6098,19 +5185,19 @@
         <v>BC-MAIN-6b4800fe</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F10" s="6">
         <f>market_shares_calc!F9</f>
         <v>0.20027847898605389</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>83</v>
@@ -6120,19 +5207,19 @@
         <v>BC-MAIN-6b4800fe</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F11" s="5">
         <f>market_shares_calc!J9</f>
         <v>0.37725640072201061</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>89</v>
@@ -6142,16 +5229,16 @@
         <v>QC-MAIN-c0660aec</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F12" s="6">
         <f>market_shares_calc!F10</f>
         <v>1.4058926821320202E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>1</v>
@@ -6164,41 +5251,41 @@
         <v>QC-MAIN-c0660aec</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F13" s="5">
         <f>market_shares_calc!E10</f>
         <v>2.1875988282066609E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" t="str">
         <f>site_selection!A11</f>
         <v>ON-MAIN-6e9be24e</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F14" s="5">
         <f>market_shares_calc!E11</f>
         <v>2.1885675871869278E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>96</v>
@@ -6208,19 +5295,19 @@
         <v>BC-MAIN-bf503b6b</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F15" s="6">
         <f>market_shares_calc!F12</f>
         <v>0.36878936168397713</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>96</v>
@@ -6230,14 +5317,14 @@
         <v>BC-MAIN-bf503b6b</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F16" s="5">
         <f>market_shares_calc!J12</f>
         <v>0.6227435992779895</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>99</v>
       </c>
@@ -6252,19 +5339,19 @@
         <v>ON-MAIN-687b8c8d</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F17" s="5">
         <f>market_shares_calc!E13</f>
         <v>2.0389080148630747E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>100</v>
@@ -6274,19 +5361,19 @@
         <v>GRP-21eee27d</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F18" s="5">
         <f>market_shares_calc!H33</f>
         <v>0.4285714285714286</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>103</v>
@@ -6296,36 +5383,36 @@
         <v>ON-MAIN-f8313ebd</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F19" s="6">
         <f>market_shares_calc!F14</f>
         <v>8.1392964590409025E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="C20" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D20" t="str">
         <f>site_selection!A14</f>
         <v>ON-MAIN-f8313ebd</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F20" s="5">
         <f>market_shares_calc!I14</f>
         <v>0.4768703163206599</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>108</v>
       </c>
@@ -6340,19 +5427,19 @@
         <v>QC-MAIN-9de9bb0d</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F21" s="5">
         <f>market_shares_calc!E15</f>
         <v>5.9654352078699303E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>111</v>
@@ -6362,16 +5449,16 @@
         <v>QC-MAIN-e51eda66</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F22" s="6">
         <f>market_shares_calc!F16</f>
         <v>9.2844175892855107E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>1</v>
@@ -6384,19 +5471,19 @@
         <v>QC-MAIN-e51eda66</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F23" s="5">
         <f>market_shares_calc!E16</f>
         <v>4.7926286288182088E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>111</v>
@@ -6406,14 +5493,14 @@
         <v>QC-MAIN-e51eda66</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="5">
         <f>market_shares_calc!I16</f>
         <v>9.5157106011456591E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>116</v>
       </c>
@@ -6428,14 +5515,14 @@
         <v>ON-MAIN-1f126a43</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F25" s="5">
         <f>market_shares_calc!E17</f>
         <v>3.546132748681375E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>160</v>
       </c>
@@ -6450,14 +5537,14 @@
         <v>GRP-0a2c0d69</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F26" s="5">
         <f>market_shares_calc!E34</f>
         <v>8.6376712978073894E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>121</v>
       </c>
@@ -6472,19 +5559,19 @@
         <v>NU-MAIN-8b0264c9</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F27" s="5">
         <f>market_shares_calc!E19</f>
         <v>6.0692581418687316E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>123</v>
@@ -6494,19 +5581,19 @@
         <v>BC-MAIN-ed23117f</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F28" s="6">
         <f>market_shares_calc!F20</f>
         <v>0.10105731865444752</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>126</v>
@@ -6516,14 +5603,14 @@
         <v>BC-MAIN-3f490561</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F29" s="6">
         <f>market_shares_calc!F21</f>
         <v>4.9244655375486092E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>129</v>
       </c>
@@ -6538,19 +5625,19 @@
         <v>ON-MAIN-fefeaee4</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F30" s="5">
         <f>market_shares_calc!E22</f>
         <v>2.7930246778946222E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>131</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>131</v>
@@ -6560,19 +5647,19 @@
         <v>BC-MAIN-aa76f6f2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F31" s="6">
         <f>market_shares_calc!F23</f>
         <v>7.7432299379599959E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>133</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>133</v>
@@ -6582,14 +5669,14 @@
         <v>QC-MAIN-5ce331b8</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F32" s="5">
         <f>market_shares_calc!G24</f>
         <v>0.56009717348552035</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>163</v>
       </c>
@@ -6604,19 +5691,19 @@
         <v>GRP-0d911886</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F33" s="5">
         <f>market_shares_calc!E35</f>
         <v>4.0343689791811209E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>136</v>
@@ -6626,14 +5713,14 @@
         <v>QC-MAIN-a97821c0</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F34" s="5">
         <f>market_shares_calc!G25</f>
         <v>0.23360197431843596</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>140</v>
       </c>
@@ -6648,35 +5735,35 @@
         <v>ON-MAIN-0aadf28f</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F35" s="5">
         <f>market_shares_calc!E26</f>
         <v>3.9373113716242782E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F36" s="5">
         <f>market_shares_calc!E27</f>
         <v>1.7487437844373552E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>167</v>
       </c>
@@ -6691,19 +5778,19 @@
         <v>GRP-14bfbb82</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F37" s="5">
         <f>market_shares_calc!E37</f>
         <v>6.0138476356201053E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>169</v>
@@ -6713,16 +5800,16 @@
         <v>GRP-a13779f8</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F38" s="6">
         <f>market_shares_calc!F38</f>
         <v>4.3772127948311111E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>1</v>
@@ -6735,19 +5822,19 @@
         <v>GRP-a13779f8</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F39" s="5">
         <f>market_shares_calc!E38</f>
         <v>0.16123293558082286</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>169</v>
@@ -6757,36 +5844,36 @@
         <v>GRP-a13779f8</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F40" s="5">
         <f>market_shares_calc!I38</f>
         <v>0.42797257766788344</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="D41" t="str">
         <f>site_selection!A28</f>
         <v>MB-MAIN-e0a6250e</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F41" s="5">
         <f>market_shares_calc!G28</f>
         <v>7.6157791231249758E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>165</v>
       </c>
@@ -6801,19 +5888,19 @@
         <v>GRP-147b3123</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F42" s="13">
         <f>market_shares_calc!E36</f>
         <v>2.0621832205121964E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>146</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>146</v>
@@ -6823,14 +5910,14 @@
         <v>NL-MAIN-2d8801d6</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F43" s="5">
         <f>market_shares_calc!G29</f>
         <v>0.13014306096479389</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>149</v>
       </c>
@@ -6845,22 +5932,22 @@
         <v>QC-MAIN-02884fb5</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F44" s="5">
         <f>market_shares_calc!E30</f>
         <v>2.0133673558641044E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
     </row>
@@ -6874,15 +5961,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAA6255D-77F9-4269-B2CE-74E3D78C471C}">
   <dimension ref="A1:S40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.28515625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.26953125" customWidth="1"/>
+    <col min="4" max="4" width="28.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -6893,10 +5980,10 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -6917,7 +6004,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>site_selection!C2</f>
         <v>Brucejack</v>
@@ -6955,7 +6042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>site_selection!C3</f>
         <v>Canadian Malartic</v>
@@ -6993,7 +6080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>site_selection!C4</f>
         <v>Casa Berardi</v>
@@ -7031,7 +6118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>site_selection!C5</f>
         <v>Copper Mountain</v>
@@ -7069,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>site_selection!C6</f>
         <v>Detour Lake</v>
@@ -7107,7 +6194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>site_selection!C7</f>
         <v>Eagle River</v>
@@ -7145,7 +6232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>site_selection!C8</f>
         <v>Éléonore</v>
@@ -7183,7 +6270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>site_selection!C9</f>
         <v>Gibraltar</v>
@@ -7221,7 +6308,7 @@
         <v>0.37725640072201061</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>site_selection!C10</f>
         <v>Goldex</v>
@@ -7259,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>site_selection!C11</f>
         <v>Hemlo (Williams)</v>
@@ -7297,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>site_selection!C12</f>
         <v>Highland Valley</v>
@@ -7335,7 +6422,7 @@
         <v>0.6227435992779895</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>site_selection!C13</f>
         <v>Island</v>
@@ -7373,7 +6460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>site_selection!C14</f>
         <v>Kidd Creek</v>
@@ -7411,7 +6498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>site_selection!C15</f>
         <v>Kiena</v>
@@ -7449,7 +6536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>site_selection!C16</f>
         <v>LaRonde</v>
@@ -7487,7 +6574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>site_selection!C17</f>
         <v>Macassa</v>
@@ -7525,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>site_selection!C18</f>
         <v>Magino</v>
@@ -7563,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>site_selection!C19</f>
         <v>Meliadine</v>
@@ -7601,7 +6688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>site_selection!C20</f>
         <v>Mount Milligan</v>
@@ -7639,7 +6726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>site_selection!C21</f>
         <v>Mount Polley</v>
@@ -7677,7 +6764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>site_selection!C22</f>
         <v>Musselwhite</v>
@@ -7715,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>site_selection!C23</f>
         <v>New Afton</v>
@@ -7753,7 +6840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>site_selection!C24</f>
         <v>Nunavik Nickel</v>
@@ -7791,7 +6878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>site_selection!C25</f>
         <v>Raglan</v>
@@ -7829,7 +6916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>site_selection!C26</f>
         <v>Rainy River</v>
@@ -7867,9 +6954,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27" t="str">
         <f>site_selection!I27</f>
@@ -7899,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>site_selection!C28</f>
         <v>Thompson (T-1 and T-3)</v>
@@ -7937,7 +7024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>site_selection!C29</f>
         <v>Voisey’s Bay</v>
@@ -7975,7 +7062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>site_selection!C30</f>
         <v>Westwood-Doyon</v>
@@ -8013,7 +7100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>site_selection!C31</f>
         <v>Young-Davidson</v>
@@ -8051,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B32" t="str">
         <f>site_selection!D32</f>
         <v>Cigar Lake + McClean Lake</v>
@@ -8089,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B33" t="str">
         <f>site_selection!D33</f>
         <v>Key Lake + McArthur River</v>
@@ -8127,7 +7214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B34" t="str">
         <f>site_selection!D34</f>
         <v>Meadowbank complex</v>
@@ -8165,7 +7252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B35" t="str">
         <f>site_selection!D35</f>
         <v>Porcupine complex</v>
@@ -8203,7 +7290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="11"/>
       <c r="B36" s="11" t="str">
         <f>site_selection!D36</f>
@@ -8242,7 +7329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B37" t="str">
         <f>site_selection!D37</f>
         <v>Seabee Gold Operation</v>
@@ -8280,7 +7367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B38" t="str">
         <f>site_selection!D38</f>
         <v>Snow Lake</v>
@@ -8318,7 +7405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E40" s="29">
         <f>SUM(E2:E38)</f>
         <v>0.99999999999999967</v>
@@ -8365,49 +7452,49 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44BE7A8F-47FB-4B9C-94EC-15BDC8617CF8}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="255.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>274</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>275</v>
       </c>
       <c r="D2" s="14">
         <v>80</v>
@@ -8419,15 +7506,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>274</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>275</v>
       </c>
       <c r="D3" s="14">
         <v>5</v>
@@ -8439,15 +7526,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D4" s="14">
         <v>20</v>
@@ -8459,18 +7546,18 @@
         <v>30</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D5" s="14">
         <v>50</v>
@@ -8482,18 +7569,18 @@
         <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -8505,18 +7592,18 @@
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7">
         <v>50</v>
@@ -8528,15 +7615,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D8">
         <v>45</v>
@@ -8548,31 +7635,31 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F9" s="2">
         <v>85</v>
       </c>
       <c r="G9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -8587,45 +7674,45 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9325684C-05D3-4E6D-AF51-2A5AC845A568}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="150.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="150.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>176</v>
-      </c>
-      <c r="B2" t="s">
-        <v>177</v>
       </c>
       <c r="C2">
         <v>9.3391084359322303</v>
       </c>
       <c r="D2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>179</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -8634,12 +7721,12 @@
         <v>6.9</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -8648,12 +7735,12 @@
         <v>51793.135000000002</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B5" t="s">
         <v>47</v>
@@ -8662,26 +7749,26 @@
         <v>15.31</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" t="s">
         <v>182</v>
-      </c>
-      <c r="B6" t="s">
-        <v>183</v>
       </c>
       <c r="C6">
         <v>2.0625835737454548</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -8690,12 +7777,12 @@
         <v>29.24</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -8704,10 +7791,10 @@
         <v>15.59</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>109</v>
       </c>
@@ -8716,36 +7803,36 @@
         <v>51438.79</v>
       </c>
       <c r="D9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>187</v>
       </c>
       <c r="C10">
         <f>72449*0.71</f>
         <v>51438.79</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" t="s">
         <v>188</v>
-      </c>
-      <c r="B11" t="s">
-        <v>189</v>
       </c>
       <c r="C11">
         <v>672.13</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>5</v>
       </c>
@@ -8753,12 +7840,12 @@
         <v>0.17169999999999999</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -8767,21 +7854,21 @@
         <v>2.5793145391818189</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" t="s">
         <v>191</v>
-      </c>
-      <c r="B14" t="s">
-        <v>192</v>
       </c>
       <c r="C14">
         <v>78.78</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
